--- a/data/externalStats/File1/RPT_RPT4025233122954TF_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT4025233122954TF_externalStats.xlsx
@@ -2335,7 +2335,7 @@
         <v>5520.587381943594</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>9.113706901155732</v>
+        <v>9.11370690115573</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>7437.951394213698</v>
+        <v>7437.951394213699</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>9.113706901155732</v>
@@ -3923,7 +3923,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>4.667505273660632</v>
@@ -4235,7 +4235,7 @@
         <v>54.53380059397892</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>69.3558931547049</v>
+        <v>69.35589315470493</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>187.2786735950308</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>61.29731101430601</v>
+        <v>61.29731101430602</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>52.49392299680903</v>
@@ -4259,10 +4259,10 @@
         <v>180.7431053864041</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>55.56519857062769</v>
+        <v>55.5651985706277</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>52.05310459182851</v>
+        <v>52.0531045918285</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>64.70313699389321</v>
@@ -4718,31 +4718,31 @@
         <v>0.6391404946152761</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.1008395309933476</v>
+        <v>0.1008395309933405</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>37.02512461833565</v>
+        <v>37.02512461833562</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5699737037045622</v>
+        <v>0.569973703704548</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.08792176194483403</v>
+        <v>0.08792176194481982</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>36.51166479234165</v>
+        <v>36.51166479234163</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5701869378585513</v>
@@ -4805,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
         <v>88.99385725072311</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>290.5599198854284</v>
@@ -5147,13 +5147,13 @@
         <v>54.91674088928271</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>88.06058310600032</v>
+        <v>88.06058310600034</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>283.8884273024006</v>
+        <v>283.8884273024005</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>74.29992075915311</v>
@@ -6559,7 +6559,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>4.667505273660632</v>
@@ -6815,7 +6815,7 @@
         <v>69.28306252089106</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>82.97522275223484</v>
+        <v>82.97522275223487</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -7217,13 +7217,13 @@
         <v>0.1008395309933405</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>36.29817516126955</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>42.40614569957291</v>
+        <v>42.40614569957289</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.569973703704548</v>
@@ -7232,10 +7232,10 @@
         <v>0.08792176194482693</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>43.42474306318525</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7574,10 +7574,10 @@
         <v>104.0482625657576</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>338.4402658587867</v>
+        <v>338.4402658587866</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>85.55188909988993</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>51479.2874751646</v>
+        <v>51479.28747516461</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>42.88056699746012</v>
@@ -8782,7 +8782,7 @@
         <v>8558.030471186486</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>6.942429228798463</v>
+        <v>6.942429228798462</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>9.141959392549317</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>60099.70267713495</v>
+        <v>60099.70267713496</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>49.86769475813242</v>
@@ -10237,7 +10237,7 @@
         <v>26967.75168511963</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>26.54016974502199</v>
+        <v>26.54016974502198</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -10447,7 +10447,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>4.667505273660632</v>
@@ -10759,7 +10759,7 @@
         <v>54.53380059397892</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>69.3558931547049</v>
+        <v>69.35589315470493</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -10768,7 +10768,7 @@
         <v>187.2786735950308</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>61.29731101430601</v>
+        <v>61.29731101430602</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>52.49392299680903</v>
@@ -10783,10 +10783,10 @@
         <v>180.7431053864041</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>55.56519857062769</v>
+        <v>55.5651985706277</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>52.05310459182851</v>
+        <v>52.0531045918285</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>64.70313699389321</v>
@@ -11242,31 +11242,31 @@
         <v>0.6391404946152761</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.1008395309933476</v>
+        <v>0.1008395309933405</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>37.02512461833565</v>
+        <v>37.02512461833562</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5699737037045622</v>
+        <v>0.569973703704548</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.08792176194483403</v>
+        <v>0.08792176194481982</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>36.51166479234165</v>
+        <v>36.51166479234163</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5701869378585513</v>
@@ -11329,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11659,7 +11659,7 @@
         <v>88.99385725072311</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>290.5599198854284</v>
@@ -11671,13 +11671,13 @@
         <v>54.91674088928271</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>88.06058310600032</v>
+        <v>88.06058310600034</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>283.8884273024006</v>
+        <v>283.8884273024005</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>74.29992075915311</v>
@@ -13083,7 +13083,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>4.667505273660632</v>
@@ -13339,7 +13339,7 @@
         <v>69.28306252089106</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>82.97522275223484</v>
+        <v>82.97522275223487</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -13741,13 +13741,13 @@
         <v>0.1008395309933405</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>36.29817516126955</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>42.40614569957291</v>
+        <v>42.40614569957289</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.569973703704548</v>
@@ -13756,10 +13756,10 @@
         <v>0.08792176194482693</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>43.42474306318525</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -14098,10 +14098,10 @@
         <v>104.0482625657576</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>338.4402658587867</v>
+        <v>338.4402658587866</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>85.55188909988993</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>64043.47173804005</v>
+        <v>64043.47173804007</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>51.41716743555845</v>
+        <v>51.41716743555844</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15460,7 +15460,7 @@
         <v>6048.064903563136</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>9.146347533057741</v>
+        <v>9.146347533057739</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -16971,7 +16971,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>4.667505273660632</v>
@@ -17283,7 +17283,7 @@
         <v>54.53380059397892</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>69.3558931547049</v>
+        <v>69.35589315470493</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -17292,7 +17292,7 @@
         <v>187.2786735950308</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>61.29731101430601</v>
+        <v>61.29731101430602</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>52.49392299680903</v>
@@ -17307,10 +17307,10 @@
         <v>180.7431053864041</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>55.56519857062769</v>
+        <v>55.5651985706277</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>52.05310459182851</v>
+        <v>52.0531045918285</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>64.70313699389321</v>
@@ -17766,31 +17766,31 @@
         <v>0.6391404946152761</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.1008395309933476</v>
+        <v>0.1008395309933405</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>37.02512461833565</v>
+        <v>37.02512461833562</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5699737037045622</v>
+        <v>0.569973703704548</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.08792176194483403</v>
+        <v>0.08792176194481982</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>36.51166479234165</v>
+        <v>36.51166479234163</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5701869378585513</v>
@@ -17853,10 +17853,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -18183,7 +18183,7 @@
         <v>88.99385725072311</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>290.5599198854284</v>
@@ -18195,13 +18195,13 @@
         <v>54.91674088928271</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>88.06058310600032</v>
+        <v>88.06058310600034</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>283.8884273024006</v>
+        <v>283.8884273024005</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>74.29992075915311</v>
@@ -19607,7 +19607,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>4.667505273660632</v>
@@ -19863,7 +19863,7 @@
         <v>69.28306252089106</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>82.97522275223484</v>
+        <v>82.97522275223487</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -20265,13 +20265,13 @@
         <v>0.1008395309933405</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>36.29817516126955</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>42.40614569957291</v>
+        <v>42.40614569957289</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.569973703704548</v>
@@ -20280,10 +20280,10 @@
         <v>0.08792176194482693</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>43.42474306318525</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20622,10 +20622,10 @@
         <v>104.0482625657576</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>338.4402658587867</v>
+        <v>338.4402658587866</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>85.55188909988993</v>
@@ -21981,10 +21981,10 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>9.116896294001295</v>
+        <v>9.116896294001297</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -23269,7 +23269,7 @@
         <v>87555.74838878366</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -23495,7 +23495,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>4.667505273660632</v>
@@ -23807,7 +23807,7 @@
         <v>54.53380059397892</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>69.3558931547049</v>
+        <v>69.35589315470493</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -23816,7 +23816,7 @@
         <v>187.2786735950308</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>61.29731101430601</v>
+        <v>61.29731101430602</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>52.49392299680903</v>
@@ -23831,10 +23831,10 @@
         <v>180.7431053864041</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>55.56519857062769</v>
+        <v>55.5651985706277</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>52.05310459182851</v>
+        <v>52.0531045918285</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>64.70313699389321</v>
@@ -24290,31 +24290,31 @@
         <v>0.6391404946152761</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.1008395309933476</v>
+        <v>0.1008395309933405</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>37.02512461833565</v>
+        <v>37.02512461833562</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5699737037045622</v>
+        <v>0.569973703704548</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.08792176194483403</v>
+        <v>0.08792176194481982</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>36.51166479234165</v>
+        <v>36.51166479234163</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5701869378585513</v>
@@ -24377,10 +24377,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24698,7 +24698,7 @@
         <v>88.99385725072311</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>290.5599198854284</v>
@@ -24710,13 +24710,13 @@
         <v>54.91674088928271</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>88.06058310600032</v>
+        <v>88.06058310600034</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>283.8884273024006</v>
+        <v>283.8884273024005</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>74.29992075915311</v>
@@ -26122,7 +26122,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>4.667505273660632</v>
@@ -26378,7 +26378,7 @@
         <v>69.28306252089106</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>82.97522275223484</v>
+        <v>82.97522275223487</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -26780,13 +26780,13 @@
         <v>0.1008395309933405</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>36.29817516126955</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>42.40614569957291</v>
+        <v>42.40614569957289</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.569973703704548</v>
@@ -26795,10 +26795,10 @@
         <v>0.08792176194482693</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>43.42474306318525</v>
@@ -26865,10 +26865,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -27137,10 +27137,10 @@
         <v>104.0482625657576</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>338.4402658587867</v>
+        <v>338.4402658587866</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>85.55188909988993</v>
@@ -28188,7 +28188,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>97701.03174199554</v>
+        <v>97701.03174199555</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>73.90391183428737</v>
@@ -29934,7 +29934,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>9.087539887934609</v>
@@ -29980,7 +29980,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>4.667505273660632</v>
@@ -30292,7 +30292,7 @@
         <v>54.53380059397892</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>69.3558931547049</v>
+        <v>69.35589315470493</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
@@ -30301,7 +30301,7 @@
         <v>187.2786735950308</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>61.29731101430601</v>
+        <v>61.29731101430602</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>52.49392299680903</v>
@@ -30316,10 +30316,10 @@
         <v>180.7431053864041</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>55.56519857062769</v>
+        <v>55.5651985706277</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>52.05310459182851</v>
+        <v>52.0531045918285</v>
       </c>
       <c r="X57" s="131" t="n">
         <v>64.70313699389321</v>
@@ -30766,31 +30766,31 @@
         <v>0.6391404946152761</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>0.1008395309933476</v>
+        <v>0.1008395309933405</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>37.02512461833565</v>
+        <v>37.02512461833562</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>0.5699737037045622</v>
+        <v>0.569973703704548</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>0.08792176194483403</v>
+        <v>0.08792176194481982</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>36.51166479234165</v>
+        <v>36.51166479234163</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>0.5701869378585513</v>
@@ -30853,10 +30853,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -30868,10 +30868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -31165,7 +31165,7 @@
         <v>88.99385725072311</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>30.91715408003228</v>
+        <v>30.91715408003229</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>290.5599198854284</v>
@@ -31177,13 +31177,13 @@
         <v>54.91674088928271</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>88.06058310600032</v>
+        <v>88.06058310600034</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>30.34749389162891</v>
+        <v>30.3474938916289</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>283.8884273024006</v>
+        <v>283.8884273024005</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>74.29992075915311</v>
@@ -32589,7 +32589,7 @@
         <v>3.110656979054278</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>2.334896130528857</v>
+        <v>2.334896130528858</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>4.667505273660632</v>
@@ -32845,7 +32845,7 @@
         <v>69.28306252089106</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>82.97522275223484</v>
+        <v>82.97522275223487</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -33247,13 +33247,13 @@
         <v>0.1008395309933405</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>5.367990512694746</v>
+        <v>5.367990512694718</v>
       </c>
       <c r="M99" s="131" t="n">
         <v>36.29817516126955</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>42.40614569957291</v>
+        <v>42.40614569957289</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>0.569973703704548</v>
@@ -33262,10 +33262,10 @@
         <v>0.08792176194482693</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>5.506275435063344</v>
+        <v>5.506275435063358</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>43.42474306318525</v>
@@ -33332,10 +33332,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33604,10 +33604,10 @@
         <v>104.0482625657576</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>37.26057216247253</v>
+        <v>37.26057216247252</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>338.4402658587867</v>
+        <v>338.4402658587866</v>
       </c>
       <c r="V104" s="142" t="n">
         <v>85.55188909988993</v>
